--- a/RB2/GroupRB Billables for Start/daily/Daily 2026-09-07.xlsx
+++ b/RB2/GroupRB Billables for Start/daily/Daily 2026-09-07.xlsx
@@ -372,42 +372,62 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0790168</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAR</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAR SEO Tracking — staging verification</t>
+        </is>
+      </c>
+      <c r="D17" s="6">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Totals by Client</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CFB</t>
-        </is>
-      </c>
-      <c r="D19" s="8">
-        <v>5.25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAR</t>
+          <t xml:space="preserve">CFB</t>
         </is>
       </c>
       <c r="D20" s="8">
-        <v>2.25</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAR</t>
+        </is>
+      </c>
+      <c r="D21" s="8">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Grand Total</t>
         </is>
       </c>
-      <c r="D21" s="10">
-        <v>7.5</v>
+      <c r="D22" s="10">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
